--- a/artfynd/A 25384-2021 artfynd.xlsx
+++ b/artfynd/A 25384-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 25384-2021 artfynd.xlsx
+++ b/artfynd/A 25384-2021 artfynd.xlsx
@@ -1497,12 +1497,7 @@
         <v>113679334</v>
       </c>
       <c r="B9" t="n">
-        <v>74585</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75416</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1594,12 +1589,12 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -1608,12 +1603,7 @@
         <v>113679318</v>
       </c>
       <c r="B10" t="n">
-        <v>74585</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75416</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1705,12 +1695,12 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -1719,12 +1709,7 @@
         <v>113679313</v>
       </c>
       <c r="B11" t="n">
-        <v>74585</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75416</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1816,12 +1801,12 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -1830,12 +1815,7 @@
         <v>113679332</v>
       </c>
       <c r="B12" t="n">
-        <v>79587</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80444</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,12 +1907,12 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -1941,12 +1921,7 @@
         <v>113679309</v>
       </c>
       <c r="B13" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79310</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2038,12 +2013,12 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -2052,12 +2027,7 @@
         <v>113679317</v>
       </c>
       <c r="B14" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80415</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,12 +2119,12 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -2163,12 +2133,7 @@
         <v>113679325</v>
       </c>
       <c r="B15" t="n">
-        <v>74585</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75416</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2260,12 +2225,12 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -2274,12 +2239,7 @@
         <v>113679324</v>
       </c>
       <c r="B16" t="n">
-        <v>79518</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80375</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2371,12 +2331,12 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -2385,12 +2345,7 @@
         <v>113679305</v>
       </c>
       <c r="B17" t="n">
-        <v>78541</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79342</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2482,12 +2437,12 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -2496,12 +2451,7 @@
         <v>113679337</v>
       </c>
       <c r="B18" t="n">
-        <v>74585</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75416</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2593,12 +2543,12 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -2607,12 +2557,7 @@
         <v>113679295</v>
       </c>
       <c r="B19" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79310</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,12 +2649,12 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -2718,12 +2663,7 @@
         <v>113680810</v>
       </c>
       <c r="B20" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91847</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2815,12 +2755,12 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Helene Andersson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -2829,12 +2769,7 @@
         <v>113680806</v>
       </c>
       <c r="B21" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91884</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2926,12 +2861,12 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Helene Andersson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -2940,12 +2875,7 @@
         <v>113679311</v>
       </c>
       <c r="B22" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80415</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3037,12 +2967,12 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -3051,12 +2981,7 @@
         <v>113679327</v>
       </c>
       <c r="B23" t="n">
-        <v>74585</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75416</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3148,12 +3073,12 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -3162,12 +3087,7 @@
         <v>113680809</v>
       </c>
       <c r="B24" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91847</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,12 +3179,12 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Helene Andersson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -3273,12 +3193,7 @@
         <v>113680807</v>
       </c>
       <c r="B25" t="n">
-        <v>90346</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91898</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3370,12 +3285,12 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Helene Andersson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -3384,12 +3299,7 @@
         <v>113680811</v>
       </c>
       <c r="B26" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91884</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3481,12 +3391,12 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Helene Andersson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -3495,12 +3405,7 @@
         <v>113679338</v>
       </c>
       <c r="B27" t="n">
-        <v>80429</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81295</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3592,12 +3497,12 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -3606,12 +3511,7 @@
         <v>113679344</v>
       </c>
       <c r="B28" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79310</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3703,12 +3603,12 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -3717,12 +3617,7 @@
         <v>113679343</v>
       </c>
       <c r="B29" t="n">
-        <v>79518</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80375</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3814,12 +3709,12 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -3828,12 +3723,7 @@
         <v>113679307</v>
       </c>
       <c r="B30" t="n">
-        <v>78541</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79342</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3925,12 +3815,12 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -3939,12 +3829,7 @@
         <v>113679347</v>
       </c>
       <c r="B31" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79310</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4036,12 +3921,12 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -4050,12 +3935,7 @@
         <v>113680802</v>
       </c>
       <c r="B32" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91847</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4147,12 +4027,12 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Helene Andersson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -4161,12 +4041,7 @@
         <v>113679346</v>
       </c>
       <c r="B33" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79310</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4258,12 +4133,12 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -4272,12 +4147,7 @@
         <v>113679345</v>
       </c>
       <c r="B34" t="n">
-        <v>74647</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4369,12 +4239,12 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -4383,12 +4253,7 @@
         <v>113679301</v>
       </c>
       <c r="B35" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79310</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4480,12 +4345,12 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -4494,12 +4359,7 @@
         <v>113679335</v>
       </c>
       <c r="B36" t="n">
-        <v>74585</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75416</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4591,12 +4451,12 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -4605,12 +4465,7 @@
         <v>113679300</v>
       </c>
       <c r="B37" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79310</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4702,12 +4557,12 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -4716,12 +4571,7 @@
         <v>113679297</v>
       </c>
       <c r="B38" t="n">
-        <v>74585</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75416</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4813,12 +4663,12 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -4827,12 +4677,7 @@
         <v>113679328</v>
       </c>
       <c r="B39" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79310</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4924,12 +4769,12 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -4938,12 +4783,7 @@
         <v>113679329</v>
       </c>
       <c r="B40" t="n">
-        <v>79518</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80375</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5035,12 +4875,12 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -5049,12 +4889,7 @@
         <v>113679322</v>
       </c>
       <c r="B41" t="n">
-        <v>79518</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80375</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5146,12 +4981,12 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -5160,12 +4995,7 @@
         <v>113679308</v>
       </c>
       <c r="B42" t="n">
-        <v>78541</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79342</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5257,12 +5087,12 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -5271,12 +5101,7 @@
         <v>113679314</v>
       </c>
       <c r="B43" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79310</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5368,12 +5193,12 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -5382,12 +5207,7 @@
         <v>113680812</v>
       </c>
       <c r="B44" t="n">
-        <v>90343</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91895</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5479,12 +5299,12 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Helene Andersson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -5493,12 +5313,7 @@
         <v>113680808</v>
       </c>
       <c r="B45" t="n">
-        <v>90346</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91898</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5590,12 +5405,12 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Helene Andersson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -5604,12 +5419,7 @@
         <v>113679312</v>
       </c>
       <c r="B46" t="n">
-        <v>74585</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75416</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5701,12 +5511,12 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -5715,12 +5525,7 @@
         <v>113679341</v>
       </c>
       <c r="B47" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80415</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5812,12 +5617,12 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -5826,12 +5631,7 @@
         <v>113679340</v>
       </c>
       <c r="B48" t="n">
-        <v>79464</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80319</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5923,12 +5723,12 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -5937,12 +5737,7 @@
         <v>113677135</v>
       </c>
       <c r="B49" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6034,12 +5829,12 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -6048,12 +5843,7 @@
         <v>113677134</v>
       </c>
       <c r="B50" t="n">
-        <v>4763</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6145,12 +5935,12 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -6159,12 +5949,7 @@
         <v>113679323</v>
       </c>
       <c r="B51" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79310</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6256,12 +6041,12 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -6270,12 +6055,7 @@
         <v>113680803</v>
       </c>
       <c r="B52" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91847</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6367,12 +6147,12 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Helene Andersson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -6381,12 +6161,7 @@
         <v>113679316</v>
       </c>
       <c r="B53" t="n">
-        <v>79518</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80375</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6478,12 +6253,12 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -6492,12 +6267,7 @@
         <v>113679333</v>
       </c>
       <c r="B54" t="n">
-        <v>79518</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80375</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6589,12 +6359,12 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -6603,12 +6373,7 @@
         <v>113679321</v>
       </c>
       <c r="B55" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79310</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6700,12 +6465,12 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -6714,12 +6479,7 @@
         <v>113679303</v>
       </c>
       <c r="B56" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79310</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6811,12 +6571,12 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -6825,12 +6585,7 @@
         <v>113679302</v>
       </c>
       <c r="B57" t="n">
-        <v>74585</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75416</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6922,12 +6677,12 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -6936,12 +6691,7 @@
         <v>113679298</v>
       </c>
       <c r="B58" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79310</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7033,12 +6783,12 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -7047,12 +6797,7 @@
         <v>113680814</v>
       </c>
       <c r="B59" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83156</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7144,12 +6889,12 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Helene Andersson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -7158,12 +6903,7 @@
         <v>113679296</v>
       </c>
       <c r="B60" t="n">
-        <v>74585</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75416</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7255,12 +6995,12 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -7269,12 +7009,7 @@
         <v>113682723</v>
       </c>
       <c r="B61" t="n">
-        <v>97671</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99112</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7366,12 +7101,12 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -7380,12 +7115,7 @@
         <v>113677136</v>
       </c>
       <c r="B62" t="n">
-        <v>5185</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7477,12 +7207,12 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -7491,12 +7221,7 @@
         <v>113679304</v>
       </c>
       <c r="B63" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79310</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7588,12 +7313,12 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -7602,12 +7327,7 @@
         <v>113679310</v>
       </c>
       <c r="B64" t="n">
-        <v>74585</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75416</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7699,12 +7419,12 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -7713,12 +7433,7 @@
         <v>113680813</v>
       </c>
       <c r="B65" t="n">
-        <v>86661</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89269</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7810,12 +7525,12 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Helene Andersson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -7824,12 +7539,7 @@
         <v>113680805</v>
       </c>
       <c r="B66" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83156</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7921,12 +7631,12 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Helene Andersson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -7935,12 +7645,7 @@
         <v>113679320</v>
       </c>
       <c r="B67" t="n">
-        <v>78758</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79566</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8032,12 +7737,12 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -8046,12 +7751,7 @@
         <v>113679331</v>
       </c>
       <c r="B68" t="n">
-        <v>79587</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80444</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8143,12 +7843,12 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -8157,12 +7857,7 @@
         <v>113679299</v>
       </c>
       <c r="B69" t="n">
-        <v>74585</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75416</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8254,12 +7949,12 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -8268,12 +7963,7 @@
         <v>113679339</v>
       </c>
       <c r="B70" t="n">
-        <v>78541</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79342</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8365,12 +8055,12 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -8379,12 +8069,7 @@
         <v>113680801</v>
       </c>
       <c r="B71" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83156</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8476,12 +8161,12 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Helene Andersson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -8490,12 +8175,7 @@
         <v>113679326</v>
       </c>
       <c r="B72" t="n">
-        <v>74585</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75416</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8587,12 +8267,12 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -8601,12 +8281,7 @@
         <v>113679342</v>
       </c>
       <c r="B73" t="n">
-        <v>74585</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75416</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8698,12 +8373,12 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -8712,12 +8387,7 @@
         <v>113679336</v>
       </c>
       <c r="B74" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79310</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8809,12 +8479,12 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -8823,12 +8493,7 @@
         <v>113680815</v>
       </c>
       <c r="B75" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91847</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8920,12 +8585,12 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Helene Andersson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -8934,12 +8599,7 @@
         <v>113678090</v>
       </c>
       <c r="B76" t="n">
-        <v>94059</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96310</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9031,12 +8691,12 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -9045,12 +8705,7 @@
         <v>113678091</v>
       </c>
       <c r="B77" t="n">
-        <v>93683</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95934</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9142,12 +8797,12 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -9156,12 +8811,7 @@
         <v>113678088</v>
       </c>
       <c r="B78" t="n">
-        <v>94059</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96310</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9253,12 +8903,12 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -9267,12 +8917,7 @@
         <v>113678089</v>
       </c>
       <c r="B79" t="n">
-        <v>94059</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96310</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9364,12 +9009,12 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -9378,12 +9023,7 @@
         <v>113678087</v>
       </c>
       <c r="B80" t="n">
-        <v>94059</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96310</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9475,12 +9115,12 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -9489,12 +9129,7 @@
         <v>113682720</v>
       </c>
       <c r="B81" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99090</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9599,12 +9234,12 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -9613,12 +9248,7 @@
         <v>113682717</v>
       </c>
       <c r="B82" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99090</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9723,12 +9353,12 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -9737,12 +9367,7 @@
         <v>113682729</v>
       </c>
       <c r="B83" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99090</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9847,12 +9472,12 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -9861,12 +9486,7 @@
         <v>113682725</v>
       </c>
       <c r="B84" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99090</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9971,12 +9591,12 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -9985,12 +9605,7 @@
         <v>113682716</v>
       </c>
       <c r="B85" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99090</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10095,12 +9710,12 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -10109,12 +9724,7 @@
         <v>113682728</v>
       </c>
       <c r="B86" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99090</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10219,12 +9829,12 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -10233,12 +9843,7 @@
         <v>113682715</v>
       </c>
       <c r="B87" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99090</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10343,12 +9948,12 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -10357,12 +9962,7 @@
         <v>113682722</v>
       </c>
       <c r="B88" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99090</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10467,12 +10067,12 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -10481,12 +10081,7 @@
         <v>113682719</v>
       </c>
       <c r="B89" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99090</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10591,12 +10186,12 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -10605,12 +10200,7 @@
         <v>113682721</v>
       </c>
       <c r="B90" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99090</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10715,12 +10305,12 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -10729,12 +10319,7 @@
         <v>113682730</v>
       </c>
       <c r="B91" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99090</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10839,12 +10424,12 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -10853,12 +10438,7 @@
         <v>113682718</v>
       </c>
       <c r="B92" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99090</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10963,12 +10543,12 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -10977,12 +10557,7 @@
         <v>113682727</v>
       </c>
       <c r="B93" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99090</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11087,12 +10662,12 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -11101,12 +10676,7 @@
         <v>113682726</v>
       </c>
       <c r="B94" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99090</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11211,12 +10781,12 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>

--- a/artfynd/A 25384-2021 artfynd.xlsx
+++ b/artfynd/A 25384-2021 artfynd.xlsx
@@ -1497,7 +1497,7 @@
         <v>113679334</v>
       </c>
       <c r="B9" t="n">
-        <v>75421</v>
+        <v>75423</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>113679318</v>
       </c>
       <c r="B10" t="n">
-        <v>75421</v>
+        <v>75423</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>113679313</v>
       </c>
       <c r="B11" t="n">
-        <v>75421</v>
+        <v>75423</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>113679332</v>
       </c>
       <c r="B12" t="n">
-        <v>80449</v>
+        <v>80451</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>113679309</v>
       </c>
       <c r="B13" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>113679317</v>
       </c>
       <c r="B14" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>113679325</v>
       </c>
       <c r="B15" t="n">
-        <v>75421</v>
+        <v>75423</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>113679324</v>
       </c>
       <c r="B16" t="n">
-        <v>80380</v>
+        <v>80382</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>113679305</v>
       </c>
       <c r="B17" t="n">
-        <v>79347</v>
+        <v>79349</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>113679337</v>
       </c>
       <c r="B18" t="n">
-        <v>75421</v>
+        <v>75423</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>113679295</v>
       </c>
       <c r="B19" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>113680810</v>
       </c>
       <c r="B20" t="n">
-        <v>91852</v>
+        <v>91855</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>113680806</v>
       </c>
       <c r="B21" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>113679311</v>
       </c>
       <c r="B22" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>113679327</v>
       </c>
       <c r="B23" t="n">
-        <v>75421</v>
+        <v>75423</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>113680809</v>
       </c>
       <c r="B24" t="n">
-        <v>91852</v>
+        <v>91855</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>113680807</v>
       </c>
       <c r="B25" t="n">
-        <v>91903</v>
+        <v>91906</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>113680811</v>
       </c>
       <c r="B26" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>113679338</v>
       </c>
       <c r="B27" t="n">
-        <v>81300</v>
+        <v>81302</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>113679344</v>
       </c>
       <c r="B28" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>113679343</v>
       </c>
       <c r="B29" t="n">
-        <v>80380</v>
+        <v>80382</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>113679307</v>
       </c>
       <c r="B30" t="n">
-        <v>79347</v>
+        <v>79349</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>113679347</v>
       </c>
       <c r="B31" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>113680802</v>
       </c>
       <c r="B32" t="n">
-        <v>91852</v>
+        <v>91855</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>113679346</v>
       </c>
       <c r="B33" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
         <v>113679345</v>
       </c>
       <c r="B34" t="n">
-        <v>83295</v>
+        <v>83297</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>113679301</v>
       </c>
       <c r="B35" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>113679335</v>
       </c>
       <c r="B36" t="n">
-        <v>75421</v>
+        <v>75423</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>113679300</v>
       </c>
       <c r="B37" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>113679297</v>
       </c>
       <c r="B38" t="n">
-        <v>75421</v>
+        <v>75423</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>113679328</v>
       </c>
       <c r="B39" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>113679329</v>
       </c>
       <c r="B40" t="n">
-        <v>80380</v>
+        <v>80382</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>113679322</v>
       </c>
       <c r="B41" t="n">
-        <v>80380</v>
+        <v>80382</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         <v>113679308</v>
       </c>
       <c r="B42" t="n">
-        <v>79347</v>
+        <v>79349</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>113679314</v>
       </c>
       <c r="B43" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>113680812</v>
       </c>
       <c r="B44" t="n">
-        <v>91900</v>
+        <v>91903</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>113680808</v>
       </c>
       <c r="B45" t="n">
-        <v>91903</v>
+        <v>91906</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         <v>113679312</v>
       </c>
       <c r="B46" t="n">
-        <v>75421</v>
+        <v>75423</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>113679341</v>
       </c>
       <c r="B47" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>113679340</v>
       </c>
       <c r="B48" t="n">
-        <v>80324</v>
+        <v>80326</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>113679323</v>
       </c>
       <c r="B51" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         <v>113680803</v>
       </c>
       <c r="B52" t="n">
-        <v>91852</v>
+        <v>91855</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>113679316</v>
       </c>
       <c r="B53" t="n">
-        <v>80380</v>
+        <v>80382</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
         <v>113679333</v>
       </c>
       <c r="B54" t="n">
-        <v>80380</v>
+        <v>80382</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>113679321</v>
       </c>
       <c r="B55" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         <v>113679303</v>
       </c>
       <c r="B56" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>113679302</v>
       </c>
       <c r="B57" t="n">
-        <v>75421</v>
+        <v>75423</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         <v>113679298</v>
       </c>
       <c r="B58" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>113680814</v>
       </c>
       <c r="B59" t="n">
-        <v>83161</v>
+        <v>83163</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>113679296</v>
       </c>
       <c r="B60" t="n">
-        <v>75421</v>
+        <v>75423</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>113682723</v>
       </c>
       <c r="B61" t="n">
-        <v>99117</v>
+        <v>99120</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>113679304</v>
       </c>
       <c r="B63" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7327,7 +7327,7 @@
         <v>113679310</v>
       </c>
       <c r="B64" t="n">
-        <v>75421</v>
+        <v>75423</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>113680813</v>
       </c>
       <c r="B65" t="n">
-        <v>89274</v>
+        <v>89277</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>113680805</v>
       </c>
       <c r="B66" t="n">
-        <v>83161</v>
+        <v>83163</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         <v>113679320</v>
       </c>
       <c r="B67" t="n">
-        <v>79571</v>
+        <v>79573</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7751,7 +7751,7 @@
         <v>113679331</v>
       </c>
       <c r="B68" t="n">
-        <v>80449</v>
+        <v>80451</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7857,7 +7857,7 @@
         <v>113679299</v>
       </c>
       <c r="B69" t="n">
-        <v>75421</v>
+        <v>75423</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>113679339</v>
       </c>
       <c r="B70" t="n">
-        <v>79347</v>
+        <v>79349</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>113680801</v>
       </c>
       <c r="B71" t="n">
-        <v>83161</v>
+        <v>83163</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8175,7 +8175,7 @@
         <v>113679326</v>
       </c>
       <c r="B72" t="n">
-        <v>75421</v>
+        <v>75423</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>113679342</v>
       </c>
       <c r="B73" t="n">
-        <v>75421</v>
+        <v>75423</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>113679336</v>
       </c>
       <c r="B74" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>113680815</v>
       </c>
       <c r="B75" t="n">
-        <v>91852</v>
+        <v>91855</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         <v>113678090</v>
       </c>
       <c r="B76" t="n">
-        <v>96315</v>
+        <v>96318</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>113678091</v>
       </c>
       <c r="B77" t="n">
-        <v>95939</v>
+        <v>95942</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>113678088</v>
       </c>
       <c r="B78" t="n">
-        <v>96315</v>
+        <v>96318</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8917,7 +8917,7 @@
         <v>113678089</v>
       </c>
       <c r="B79" t="n">
-        <v>96315</v>
+        <v>96318</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>113678087</v>
       </c>
       <c r="B80" t="n">
-        <v>96315</v>
+        <v>96318</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>113682720</v>
       </c>
       <c r="B81" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9248,7 +9248,7 @@
         <v>113682717</v>
       </c>
       <c r="B82" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>113682729</v>
       </c>
       <c r="B83" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>113682725</v>
       </c>
       <c r="B84" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         <v>113682716</v>
       </c>
       <c r="B85" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9724,7 +9724,7 @@
         <v>113682728</v>
       </c>
       <c r="B86" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         <v>113682715</v>
       </c>
       <c r="B87" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9962,7 +9962,7 @@
         <v>113682722</v>
       </c>
       <c r="B88" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10081,7 +10081,7 @@
         <v>113682719</v>
       </c>
       <c r="B89" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10200,7 +10200,7 @@
         <v>113682721</v>
       </c>
       <c r="B90" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         <v>113682730</v>
       </c>
       <c r="B91" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>113682718</v>
       </c>
       <c r="B92" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>113682727</v>
       </c>
       <c r="B93" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         <v>113682726</v>
       </c>
       <c r="B94" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 25384-2021 artfynd.xlsx
+++ b/artfynd/A 25384-2021 artfynd.xlsx
@@ -1497,7 +1497,7 @@
         <v>113679334</v>
       </c>
       <c r="B9" t="n">
-        <v>75423</v>
+        <v>75424</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>113679318</v>
       </c>
       <c r="B10" t="n">
-        <v>75423</v>
+        <v>75424</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>113679313</v>
       </c>
       <c r="B11" t="n">
-        <v>75423</v>
+        <v>75424</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>113679332</v>
       </c>
       <c r="B12" t="n">
-        <v>80451</v>
+        <v>80453</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>113679309</v>
       </c>
       <c r="B13" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>113679317</v>
       </c>
       <c r="B14" t="n">
-        <v>80422</v>
+        <v>80424</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>113679325</v>
       </c>
       <c r="B15" t="n">
-        <v>75423</v>
+        <v>75424</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>113679324</v>
       </c>
       <c r="B16" t="n">
-        <v>80382</v>
+        <v>80384</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>113679305</v>
       </c>
       <c r="B17" t="n">
-        <v>79349</v>
+        <v>79351</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>113679337</v>
       </c>
       <c r="B18" t="n">
-        <v>75423</v>
+        <v>75424</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>113679295</v>
       </c>
       <c r="B19" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>113680810</v>
       </c>
       <c r="B20" t="n">
-        <v>91855</v>
+        <v>91861</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>113680806</v>
       </c>
       <c r="B21" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>113679311</v>
       </c>
       <c r="B22" t="n">
-        <v>80422</v>
+        <v>80424</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>113679327</v>
       </c>
       <c r="B23" t="n">
-        <v>75423</v>
+        <v>75424</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>113680809</v>
       </c>
       <c r="B24" t="n">
-        <v>91855</v>
+        <v>91861</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>113680807</v>
       </c>
       <c r="B25" t="n">
-        <v>91906</v>
+        <v>91912</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>113680811</v>
       </c>
       <c r="B26" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>113679338</v>
       </c>
       <c r="B27" t="n">
-        <v>81302</v>
+        <v>81304</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>113679344</v>
       </c>
       <c r="B28" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>113679343</v>
       </c>
       <c r="B29" t="n">
-        <v>80382</v>
+        <v>80384</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>113679307</v>
       </c>
       <c r="B30" t="n">
-        <v>79349</v>
+        <v>79351</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>113679347</v>
       </c>
       <c r="B31" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>113680802</v>
       </c>
       <c r="B32" t="n">
-        <v>91855</v>
+        <v>91861</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>113679346</v>
       </c>
       <c r="B33" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
         <v>113679345</v>
       </c>
       <c r="B34" t="n">
-        <v>83297</v>
+        <v>83299</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>113679301</v>
       </c>
       <c r="B35" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>113679335</v>
       </c>
       <c r="B36" t="n">
-        <v>75423</v>
+        <v>75424</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>113679300</v>
       </c>
       <c r="B37" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>113679297</v>
       </c>
       <c r="B38" t="n">
-        <v>75423</v>
+        <v>75424</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>113679328</v>
       </c>
       <c r="B39" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>113679329</v>
       </c>
       <c r="B40" t="n">
-        <v>80382</v>
+        <v>80384</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>113679322</v>
       </c>
       <c r="B41" t="n">
-        <v>80382</v>
+        <v>80384</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         <v>113679308</v>
       </c>
       <c r="B42" t="n">
-        <v>79349</v>
+        <v>79351</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>113679314</v>
       </c>
       <c r="B43" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>113680812</v>
       </c>
       <c r="B44" t="n">
-        <v>91903</v>
+        <v>91909</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>113680808</v>
       </c>
       <c r="B45" t="n">
-        <v>91906</v>
+        <v>91912</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         <v>113679312</v>
       </c>
       <c r="B46" t="n">
-        <v>75423</v>
+        <v>75424</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>113679341</v>
       </c>
       <c r="B47" t="n">
-        <v>80422</v>
+        <v>80424</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>113679340</v>
       </c>
       <c r="B48" t="n">
-        <v>80326</v>
+        <v>80328</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>113679323</v>
       </c>
       <c r="B51" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         <v>113680803</v>
       </c>
       <c r="B52" t="n">
-        <v>91855</v>
+        <v>91861</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>113679316</v>
       </c>
       <c r="B53" t="n">
-        <v>80382</v>
+        <v>80384</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
         <v>113679333</v>
       </c>
       <c r="B54" t="n">
-        <v>80382</v>
+        <v>80384</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>113679321</v>
       </c>
       <c r="B55" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         <v>113679303</v>
       </c>
       <c r="B56" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>113679302</v>
       </c>
       <c r="B57" t="n">
-        <v>75423</v>
+        <v>75424</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         <v>113679298</v>
       </c>
       <c r="B58" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>113680814</v>
       </c>
       <c r="B59" t="n">
-        <v>83163</v>
+        <v>83165</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>113679296</v>
       </c>
       <c r="B60" t="n">
-        <v>75423</v>
+        <v>75424</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>113682723</v>
       </c>
       <c r="B61" t="n">
-        <v>99120</v>
+        <v>99128</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>113679304</v>
       </c>
       <c r="B63" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7327,7 +7327,7 @@
         <v>113679310</v>
       </c>
       <c r="B64" t="n">
-        <v>75423</v>
+        <v>75424</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>113680813</v>
       </c>
       <c r="B65" t="n">
-        <v>89277</v>
+        <v>89283</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>113680805</v>
       </c>
       <c r="B66" t="n">
-        <v>83163</v>
+        <v>83165</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         <v>113679320</v>
       </c>
       <c r="B67" t="n">
-        <v>79573</v>
+        <v>79575</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7751,7 +7751,7 @@
         <v>113679331</v>
       </c>
       <c r="B68" t="n">
-        <v>80451</v>
+        <v>80453</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7857,7 +7857,7 @@
         <v>113679299</v>
       </c>
       <c r="B69" t="n">
-        <v>75423</v>
+        <v>75424</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>113679339</v>
       </c>
       <c r="B70" t="n">
-        <v>79349</v>
+        <v>79351</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>113680801</v>
       </c>
       <c r="B71" t="n">
-        <v>83163</v>
+        <v>83165</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8175,7 +8175,7 @@
         <v>113679326</v>
       </c>
       <c r="B72" t="n">
-        <v>75423</v>
+        <v>75424</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>113679342</v>
       </c>
       <c r="B73" t="n">
-        <v>75423</v>
+        <v>75424</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>113679336</v>
       </c>
       <c r="B74" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>113680815</v>
       </c>
       <c r="B75" t="n">
-        <v>91855</v>
+        <v>91861</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         <v>113678090</v>
       </c>
       <c r="B76" t="n">
-        <v>96318</v>
+        <v>96326</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>113678091</v>
       </c>
       <c r="B77" t="n">
-        <v>95942</v>
+        <v>95950</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>113678088</v>
       </c>
       <c r="B78" t="n">
-        <v>96318</v>
+        <v>96326</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8917,7 +8917,7 @@
         <v>113678089</v>
       </c>
       <c r="B79" t="n">
-        <v>96318</v>
+        <v>96326</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>113678087</v>
       </c>
       <c r="B80" t="n">
-        <v>96318</v>
+        <v>96326</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>113682720</v>
       </c>
       <c r="B81" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9248,7 +9248,7 @@
         <v>113682717</v>
       </c>
       <c r="B82" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>113682729</v>
       </c>
       <c r="B83" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>113682725</v>
       </c>
       <c r="B84" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         <v>113682716</v>
       </c>
       <c r="B85" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9724,7 +9724,7 @@
         <v>113682728</v>
       </c>
       <c r="B86" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         <v>113682715</v>
       </c>
       <c r="B87" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9962,7 +9962,7 @@
         <v>113682722</v>
       </c>
       <c r="B88" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10081,7 +10081,7 @@
         <v>113682719</v>
       </c>
       <c r="B89" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10200,7 +10200,7 @@
         <v>113682721</v>
       </c>
       <c r="B90" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         <v>113682730</v>
       </c>
       <c r="B91" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>113682718</v>
       </c>
       <c r="B92" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>113682727</v>
       </c>
       <c r="B93" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         <v>113682726</v>
       </c>
       <c r="B94" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 25384-2021 artfynd.xlsx
+++ b/artfynd/A 25384-2021 artfynd.xlsx
@@ -1497,7 +1497,7 @@
         <v>113679334</v>
       </c>
       <c r="B9" t="n">
-        <v>75424</v>
+        <v>75428</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>113679318</v>
       </c>
       <c r="B10" t="n">
-        <v>75424</v>
+        <v>75428</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>113679313</v>
       </c>
       <c r="B11" t="n">
-        <v>75424</v>
+        <v>75428</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>113679332</v>
       </c>
       <c r="B12" t="n">
-        <v>80453</v>
+        <v>80461</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>113679309</v>
       </c>
       <c r="B13" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>113679317</v>
       </c>
       <c r="B14" t="n">
-        <v>80424</v>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>113679325</v>
       </c>
       <c r="B15" t="n">
-        <v>75424</v>
+        <v>75428</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>113679324</v>
       </c>
       <c r="B16" t="n">
-        <v>80384</v>
+        <v>80392</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>113679305</v>
       </c>
       <c r="B17" t="n">
-        <v>79351</v>
+        <v>79359</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>113679337</v>
       </c>
       <c r="B18" t="n">
-        <v>75424</v>
+        <v>75428</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>113679295</v>
       </c>
       <c r="B19" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>113680810</v>
       </c>
       <c r="B20" t="n">
-        <v>91861</v>
+        <v>91871</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>113680806</v>
       </c>
       <c r="B21" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>113679311</v>
       </c>
       <c r="B22" t="n">
-        <v>80424</v>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>113679327</v>
       </c>
       <c r="B23" t="n">
-        <v>75424</v>
+        <v>75428</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>113680809</v>
       </c>
       <c r="B24" t="n">
-        <v>91861</v>
+        <v>91871</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>113680807</v>
       </c>
       <c r="B25" t="n">
-        <v>91912</v>
+        <v>91922</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>113680811</v>
       </c>
       <c r="B26" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>113679338</v>
       </c>
       <c r="B27" t="n">
-        <v>81304</v>
+        <v>81312</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>113679344</v>
       </c>
       <c r="B28" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>113679343</v>
       </c>
       <c r="B29" t="n">
-        <v>80384</v>
+        <v>80392</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>113679307</v>
       </c>
       <c r="B30" t="n">
-        <v>79351</v>
+        <v>79359</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>113679347</v>
       </c>
       <c r="B31" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>113680802</v>
       </c>
       <c r="B32" t="n">
-        <v>91861</v>
+        <v>91871</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>113679346</v>
       </c>
       <c r="B33" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
         <v>113679345</v>
       </c>
       <c r="B34" t="n">
-        <v>83299</v>
+        <v>83307</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>113679301</v>
       </c>
       <c r="B35" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>113679335</v>
       </c>
       <c r="B36" t="n">
-        <v>75424</v>
+        <v>75428</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>113679300</v>
       </c>
       <c r="B37" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>113679297</v>
       </c>
       <c r="B38" t="n">
-        <v>75424</v>
+        <v>75428</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>113679328</v>
       </c>
       <c r="B39" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>113679329</v>
       </c>
       <c r="B40" t="n">
-        <v>80384</v>
+        <v>80392</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>113679322</v>
       </c>
       <c r="B41" t="n">
-        <v>80384</v>
+        <v>80392</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         <v>113679308</v>
       </c>
       <c r="B42" t="n">
-        <v>79351</v>
+        <v>79359</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>113679314</v>
       </c>
       <c r="B43" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>113680812</v>
       </c>
       <c r="B44" t="n">
-        <v>91909</v>
+        <v>91919</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>113680808</v>
       </c>
       <c r="B45" t="n">
-        <v>91912</v>
+        <v>91922</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         <v>113679312</v>
       </c>
       <c r="B46" t="n">
-        <v>75424</v>
+        <v>75428</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>113679341</v>
       </c>
       <c r="B47" t="n">
-        <v>80424</v>
+        <v>80432</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>113679340</v>
       </c>
       <c r="B48" t="n">
-        <v>80328</v>
+        <v>80336</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>113679323</v>
       </c>
       <c r="B51" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         <v>113680803</v>
       </c>
       <c r="B52" t="n">
-        <v>91861</v>
+        <v>91871</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>113679316</v>
       </c>
       <c r="B53" t="n">
-        <v>80384</v>
+        <v>80392</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
         <v>113679333</v>
       </c>
       <c r="B54" t="n">
-        <v>80384</v>
+        <v>80392</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>113679321</v>
       </c>
       <c r="B55" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         <v>113679303</v>
       </c>
       <c r="B56" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>113679302</v>
       </c>
       <c r="B57" t="n">
-        <v>75424</v>
+        <v>75428</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         <v>113679298</v>
       </c>
       <c r="B58" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>113680814</v>
       </c>
       <c r="B59" t="n">
-        <v>83165</v>
+        <v>83173</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>113679296</v>
       </c>
       <c r="B60" t="n">
-        <v>75424</v>
+        <v>75428</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>113682723</v>
       </c>
       <c r="B61" t="n">
-        <v>99128</v>
+        <v>99138</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>113679304</v>
       </c>
       <c r="B63" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7327,7 +7327,7 @@
         <v>113679310</v>
       </c>
       <c r="B64" t="n">
-        <v>75424</v>
+        <v>75428</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>113680813</v>
       </c>
       <c r="B65" t="n">
-        <v>89283</v>
+        <v>89291</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>113680805</v>
       </c>
       <c r="B66" t="n">
-        <v>83165</v>
+        <v>83173</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         <v>113679320</v>
       </c>
       <c r="B67" t="n">
-        <v>79575</v>
+        <v>79583</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7751,7 +7751,7 @@
         <v>113679331</v>
       </c>
       <c r="B68" t="n">
-        <v>80453</v>
+        <v>80461</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7857,7 +7857,7 @@
         <v>113679299</v>
       </c>
       <c r="B69" t="n">
-        <v>75424</v>
+        <v>75428</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>113679339</v>
       </c>
       <c r="B70" t="n">
-        <v>79351</v>
+        <v>79359</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>113680801</v>
       </c>
       <c r="B71" t="n">
-        <v>83165</v>
+        <v>83173</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8175,7 +8175,7 @@
         <v>113679326</v>
       </c>
       <c r="B72" t="n">
-        <v>75424</v>
+        <v>75428</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>113679342</v>
       </c>
       <c r="B73" t="n">
-        <v>75424</v>
+        <v>75428</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>113679336</v>
       </c>
       <c r="B74" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>113680815</v>
       </c>
       <c r="B75" t="n">
-        <v>91861</v>
+        <v>91871</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         <v>113678090</v>
       </c>
       <c r="B76" t="n">
-        <v>96326</v>
+        <v>96336</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>113678091</v>
       </c>
       <c r="B77" t="n">
-        <v>95950</v>
+        <v>95960</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>113678088</v>
       </c>
       <c r="B78" t="n">
-        <v>96326</v>
+        <v>96336</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8917,7 +8917,7 @@
         <v>113678089</v>
       </c>
       <c r="B79" t="n">
-        <v>96326</v>
+        <v>96336</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>113678087</v>
       </c>
       <c r="B80" t="n">
-        <v>96326</v>
+        <v>96336</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>113682720</v>
       </c>
       <c r="B81" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9248,7 +9248,7 @@
         <v>113682717</v>
       </c>
       <c r="B82" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>113682729</v>
       </c>
       <c r="B83" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>113682725</v>
       </c>
       <c r="B84" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         <v>113682716</v>
       </c>
       <c r="B85" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9724,7 +9724,7 @@
         <v>113682728</v>
       </c>
       <c r="B86" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         <v>113682715</v>
       </c>
       <c r="B87" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9962,7 +9962,7 @@
         <v>113682722</v>
       </c>
       <c r="B88" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10081,7 +10081,7 @@
         <v>113682719</v>
       </c>
       <c r="B89" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10200,7 +10200,7 @@
         <v>113682721</v>
       </c>
       <c r="B90" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         <v>113682730</v>
       </c>
       <c r="B91" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>113682718</v>
       </c>
       <c r="B92" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>113682727</v>
       </c>
       <c r="B93" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         <v>113682726</v>
       </c>
       <c r="B94" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 25384-2021 artfynd.xlsx
+++ b/artfynd/A 25384-2021 artfynd.xlsx
@@ -2663,7 +2663,7 @@
         <v>113680810</v>
       </c>
       <c r="B20" t="n">
-        <v>91871</v>
+        <v>91872</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>113680806</v>
       </c>
       <c r="B21" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>113680809</v>
       </c>
       <c r="B24" t="n">
-        <v>91871</v>
+        <v>91872</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>113680807</v>
       </c>
       <c r="B25" t="n">
-        <v>91922</v>
+        <v>91923</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>113680811</v>
       </c>
       <c r="B26" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>113680802</v>
       </c>
       <c r="B32" t="n">
-        <v>91871</v>
+        <v>91872</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>113680812</v>
       </c>
       <c r="B44" t="n">
-        <v>91919</v>
+        <v>91920</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>113680808</v>
       </c>
       <c r="B45" t="n">
-        <v>91922</v>
+        <v>91923</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         <v>113680803</v>
       </c>
       <c r="B52" t="n">
-        <v>91871</v>
+        <v>91872</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>113682723</v>
       </c>
       <c r="B61" t="n">
-        <v>99138</v>
+        <v>99139</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>113680813</v>
       </c>
       <c r="B65" t="n">
-        <v>89291</v>
+        <v>89292</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>113680815</v>
       </c>
       <c r="B75" t="n">
-        <v>91871</v>
+        <v>91872</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         <v>113678090</v>
       </c>
       <c r="B76" t="n">
-        <v>96336</v>
+        <v>96337</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>113678091</v>
       </c>
       <c r="B77" t="n">
-        <v>95960</v>
+        <v>95961</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>113678088</v>
       </c>
       <c r="B78" t="n">
-        <v>96336</v>
+        <v>96337</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8917,7 +8917,7 @@
         <v>113678089</v>
       </c>
       <c r="B79" t="n">
-        <v>96336</v>
+        <v>96337</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>113678087</v>
       </c>
       <c r="B80" t="n">
-        <v>96336</v>
+        <v>96337</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>113682720</v>
       </c>
       <c r="B81" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9248,7 +9248,7 @@
         <v>113682717</v>
       </c>
       <c r="B82" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>113682729</v>
       </c>
       <c r="B83" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>113682725</v>
       </c>
       <c r="B84" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         <v>113682716</v>
       </c>
       <c r="B85" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9724,7 +9724,7 @@
         <v>113682728</v>
       </c>
       <c r="B86" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         <v>113682715</v>
       </c>
       <c r="B87" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9962,7 +9962,7 @@
         <v>113682722</v>
       </c>
       <c r="B88" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10081,7 +10081,7 @@
         <v>113682719</v>
       </c>
       <c r="B89" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10200,7 +10200,7 @@
         <v>113682721</v>
       </c>
       <c r="B90" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         <v>113682730</v>
       </c>
       <c r="B91" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>113682718</v>
       </c>
       <c r="B92" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>113682727</v>
       </c>
       <c r="B93" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         <v>113682726</v>
       </c>
       <c r="B94" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 25384-2021 artfynd.xlsx
+++ b/artfynd/A 25384-2021 artfynd.xlsx
@@ -7009,7 +7009,7 @@
         <v>113682723</v>
       </c>
       <c r="B61" t="n">
-        <v>99139</v>
+        <v>99140</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         <v>113678090</v>
       </c>
       <c r="B76" t="n">
-        <v>96337</v>
+        <v>96338</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>113678091</v>
       </c>
       <c r="B77" t="n">
-        <v>95961</v>
+        <v>95962</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>113678088</v>
       </c>
       <c r="B78" t="n">
-        <v>96337</v>
+        <v>96338</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8917,7 +8917,7 @@
         <v>113678089</v>
       </c>
       <c r="B79" t="n">
-        <v>96337</v>
+        <v>96338</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>113678087</v>
       </c>
       <c r="B80" t="n">
-        <v>96337</v>
+        <v>96338</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>113682720</v>
       </c>
       <c r="B81" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9248,7 +9248,7 @@
         <v>113682717</v>
       </c>
       <c r="B82" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>113682729</v>
       </c>
       <c r="B83" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>113682725</v>
       </c>
       <c r="B84" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         <v>113682716</v>
       </c>
       <c r="B85" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9724,7 +9724,7 @@
         <v>113682728</v>
       </c>
       <c r="B86" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         <v>113682715</v>
       </c>
       <c r="B87" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9962,7 +9962,7 @@
         <v>113682722</v>
       </c>
       <c r="B88" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10081,7 +10081,7 @@
         <v>113682719</v>
       </c>
       <c r="B89" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10200,7 +10200,7 @@
         <v>113682721</v>
       </c>
       <c r="B90" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         <v>113682730</v>
       </c>
       <c r="B91" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>113682718</v>
       </c>
       <c r="B92" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>113682727</v>
       </c>
       <c r="B93" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         <v>113682726</v>
       </c>
       <c r="B94" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 25384-2021 artfynd.xlsx
+++ b/artfynd/A 25384-2021 artfynd.xlsx
@@ -1497,7 +1497,7 @@
         <v>113679334</v>
       </c>
       <c r="B9" t="n">
-        <v>75428</v>
+        <v>75429</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>113679318</v>
       </c>
       <c r="B10" t="n">
-        <v>75428</v>
+        <v>75429</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>113679313</v>
       </c>
       <c r="B11" t="n">
-        <v>75428</v>
+        <v>75429</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>113679332</v>
       </c>
       <c r="B12" t="n">
-        <v>80461</v>
+        <v>80462</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>113679309</v>
       </c>
       <c r="B13" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>113679317</v>
       </c>
       <c r="B14" t="n">
-        <v>80432</v>
+        <v>80433</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>113679325</v>
       </c>
       <c r="B15" t="n">
-        <v>75428</v>
+        <v>75429</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>113679324</v>
       </c>
       <c r="B16" t="n">
-        <v>80392</v>
+        <v>80393</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>113679305</v>
       </c>
       <c r="B17" t="n">
-        <v>79359</v>
+        <v>79360</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>113679337</v>
       </c>
       <c r="B18" t="n">
-        <v>75428</v>
+        <v>75429</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>113679295</v>
       </c>
       <c r="B19" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>113680810</v>
       </c>
       <c r="B20" t="n">
-        <v>91872</v>
+        <v>91873</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>113680806</v>
       </c>
       <c r="B21" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>113679311</v>
       </c>
       <c r="B22" t="n">
-        <v>80432</v>
+        <v>80433</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>113679327</v>
       </c>
       <c r="B23" t="n">
-        <v>75428</v>
+        <v>75429</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>113680809</v>
       </c>
       <c r="B24" t="n">
-        <v>91872</v>
+        <v>91873</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>113680807</v>
       </c>
       <c r="B25" t="n">
-        <v>91923</v>
+        <v>91924</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>113680811</v>
       </c>
       <c r="B26" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>113679338</v>
       </c>
       <c r="B27" t="n">
-        <v>81312</v>
+        <v>81313</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>113679344</v>
       </c>
       <c r="B28" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>113679343</v>
       </c>
       <c r="B29" t="n">
-        <v>80392</v>
+        <v>80393</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>113679307</v>
       </c>
       <c r="B30" t="n">
-        <v>79359</v>
+        <v>79360</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>113679347</v>
       </c>
       <c r="B31" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>113680802</v>
       </c>
       <c r="B32" t="n">
-        <v>91872</v>
+        <v>91873</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>113679346</v>
       </c>
       <c r="B33" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
         <v>113679345</v>
       </c>
       <c r="B34" t="n">
-        <v>83307</v>
+        <v>83308</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>113679301</v>
       </c>
       <c r="B35" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>113679335</v>
       </c>
       <c r="B36" t="n">
-        <v>75428</v>
+        <v>75429</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>113679300</v>
       </c>
       <c r="B37" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>113679297</v>
       </c>
       <c r="B38" t="n">
-        <v>75428</v>
+        <v>75429</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>113679328</v>
       </c>
       <c r="B39" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>113679329</v>
       </c>
       <c r="B40" t="n">
-        <v>80392</v>
+        <v>80393</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>113679322</v>
       </c>
       <c r="B41" t="n">
-        <v>80392</v>
+        <v>80393</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         <v>113679308</v>
       </c>
       <c r="B42" t="n">
-        <v>79359</v>
+        <v>79360</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>113679314</v>
       </c>
       <c r="B43" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>113680812</v>
       </c>
       <c r="B44" t="n">
-        <v>91920</v>
+        <v>91921</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>113680808</v>
       </c>
       <c r="B45" t="n">
-        <v>91923</v>
+        <v>91924</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         <v>113679312</v>
       </c>
       <c r="B46" t="n">
-        <v>75428</v>
+        <v>75429</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>113679341</v>
       </c>
       <c r="B47" t="n">
-        <v>80432</v>
+        <v>80433</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>113679340</v>
       </c>
       <c r="B48" t="n">
-        <v>80336</v>
+        <v>80337</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>113679323</v>
       </c>
       <c r="B51" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         <v>113680803</v>
       </c>
       <c r="B52" t="n">
-        <v>91872</v>
+        <v>91873</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>113679316</v>
       </c>
       <c r="B53" t="n">
-        <v>80392</v>
+        <v>80393</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
         <v>113679333</v>
       </c>
       <c r="B54" t="n">
-        <v>80392</v>
+        <v>80393</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>113679321</v>
       </c>
       <c r="B55" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         <v>113679303</v>
       </c>
       <c r="B56" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>113679302</v>
       </c>
       <c r="B57" t="n">
-        <v>75428</v>
+        <v>75429</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         <v>113679298</v>
       </c>
       <c r="B58" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>113680814</v>
       </c>
       <c r="B59" t="n">
-        <v>83173</v>
+        <v>83174</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>113679296</v>
       </c>
       <c r="B60" t="n">
-        <v>75428</v>
+        <v>75429</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>113682723</v>
       </c>
       <c r="B61" t="n">
-        <v>99140</v>
+        <v>99141</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>113679304</v>
       </c>
       <c r="B63" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7327,7 +7327,7 @@
         <v>113679310</v>
       </c>
       <c r="B64" t="n">
-        <v>75428</v>
+        <v>75429</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>113680813</v>
       </c>
       <c r="B65" t="n">
-        <v>89292</v>
+        <v>89293</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>113680805</v>
       </c>
       <c r="B66" t="n">
-        <v>83173</v>
+        <v>83174</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         <v>113679320</v>
       </c>
       <c r="B67" t="n">
-        <v>79583</v>
+        <v>79584</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7751,7 +7751,7 @@
         <v>113679331</v>
       </c>
       <c r="B68" t="n">
-        <v>80461</v>
+        <v>80462</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7857,7 +7857,7 @@
         <v>113679299</v>
       </c>
       <c r="B69" t="n">
-        <v>75428</v>
+        <v>75429</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>113679339</v>
       </c>
       <c r="B70" t="n">
-        <v>79359</v>
+        <v>79360</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>113680801</v>
       </c>
       <c r="B71" t="n">
-        <v>83173</v>
+        <v>83174</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8175,7 +8175,7 @@
         <v>113679326</v>
       </c>
       <c r="B72" t="n">
-        <v>75428</v>
+        <v>75429</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>113679342</v>
       </c>
       <c r="B73" t="n">
-        <v>75428</v>
+        <v>75429</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>113679336</v>
       </c>
       <c r="B74" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>113680815</v>
       </c>
       <c r="B75" t="n">
-        <v>91872</v>
+        <v>91873</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         <v>113678090</v>
       </c>
       <c r="B76" t="n">
-        <v>96338</v>
+        <v>96339</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>113678091</v>
       </c>
       <c r="B77" t="n">
-        <v>95962</v>
+        <v>95963</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>113678088</v>
       </c>
       <c r="B78" t="n">
-        <v>96338</v>
+        <v>96339</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8917,7 +8917,7 @@
         <v>113678089</v>
       </c>
       <c r="B79" t="n">
-        <v>96338</v>
+        <v>96339</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>113678087</v>
       </c>
       <c r="B80" t="n">
-        <v>96338</v>
+        <v>96339</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>113682720</v>
       </c>
       <c r="B81" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9248,7 +9248,7 @@
         <v>113682717</v>
       </c>
       <c r="B82" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>113682729</v>
       </c>
       <c r="B83" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>113682725</v>
       </c>
       <c r="B84" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         <v>113682716</v>
       </c>
       <c r="B85" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9724,7 +9724,7 @@
         <v>113682728</v>
       </c>
       <c r="B86" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         <v>113682715</v>
       </c>
       <c r="B87" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9962,7 +9962,7 @@
         <v>113682722</v>
       </c>
       <c r="B88" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10081,7 +10081,7 @@
         <v>113682719</v>
       </c>
       <c r="B89" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10200,7 +10200,7 @@
         <v>113682721</v>
       </c>
       <c r="B90" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         <v>113682730</v>
       </c>
       <c r="B91" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>113682718</v>
       </c>
       <c r="B92" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>113682727</v>
       </c>
       <c r="B93" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         <v>113682726</v>
       </c>
       <c r="B94" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 25384-2021 artfynd.xlsx
+++ b/artfynd/A 25384-2021 artfynd.xlsx
@@ -2663,7 +2663,7 @@
         <v>113680810</v>
       </c>
       <c r="B20" t="n">
-        <v>91873</v>
+        <v>91875</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>113680806</v>
       </c>
       <c r="B21" t="n">
-        <v>91910</v>
+        <v>91912</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>113680809</v>
       </c>
       <c r="B24" t="n">
-        <v>91873</v>
+        <v>91875</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>113680807</v>
       </c>
       <c r="B25" t="n">
-        <v>91924</v>
+        <v>91926</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>113680811</v>
       </c>
       <c r="B26" t="n">
-        <v>91910</v>
+        <v>91912</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>113680802</v>
       </c>
       <c r="B32" t="n">
-        <v>91873</v>
+        <v>91875</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
         <v>113679345</v>
       </c>
       <c r="B34" t="n">
-        <v>83308</v>
+        <v>83310</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>113680812</v>
       </c>
       <c r="B44" t="n">
-        <v>91921</v>
+        <v>91923</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>113680808</v>
       </c>
       <c r="B45" t="n">
-        <v>91924</v>
+        <v>91926</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         <v>113680803</v>
       </c>
       <c r="B52" t="n">
-        <v>91873</v>
+        <v>91875</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>113680814</v>
       </c>
       <c r="B59" t="n">
-        <v>83174</v>
+        <v>83176</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>113682723</v>
       </c>
       <c r="B61" t="n">
-        <v>99141</v>
+        <v>99143</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>113680813</v>
       </c>
       <c r="B65" t="n">
-        <v>89293</v>
+        <v>89295</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>113680805</v>
       </c>
       <c r="B66" t="n">
-        <v>83174</v>
+        <v>83176</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>113680801</v>
       </c>
       <c r="B71" t="n">
-        <v>83174</v>
+        <v>83176</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>113680815</v>
       </c>
       <c r="B75" t="n">
-        <v>91873</v>
+        <v>91875</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         <v>113678090</v>
       </c>
       <c r="B76" t="n">
-        <v>96339</v>
+        <v>96341</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>113678091</v>
       </c>
       <c r="B77" t="n">
-        <v>95963</v>
+        <v>95965</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>113678088</v>
       </c>
       <c r="B78" t="n">
-        <v>96339</v>
+        <v>96341</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8917,7 +8917,7 @@
         <v>113678089</v>
       </c>
       <c r="B79" t="n">
-        <v>96339</v>
+        <v>96341</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>113678087</v>
       </c>
       <c r="B80" t="n">
-        <v>96339</v>
+        <v>96341</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>113682720</v>
       </c>
       <c r="B81" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9248,7 +9248,7 @@
         <v>113682717</v>
       </c>
       <c r="B82" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>113682729</v>
       </c>
       <c r="B83" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>113682725</v>
       </c>
       <c r="B84" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         <v>113682716</v>
       </c>
       <c r="B85" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9724,7 +9724,7 @@
         <v>113682728</v>
       </c>
       <c r="B86" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         <v>113682715</v>
       </c>
       <c r="B87" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9962,7 +9962,7 @@
         <v>113682722</v>
       </c>
       <c r="B88" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10081,7 +10081,7 @@
         <v>113682719</v>
       </c>
       <c r="B89" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10200,7 +10200,7 @@
         <v>113682721</v>
       </c>
       <c r="B90" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         <v>113682730</v>
       </c>
       <c r="B91" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>113682718</v>
       </c>
       <c r="B92" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>113682727</v>
       </c>
       <c r="B93" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         <v>113682726</v>
       </c>
       <c r="B94" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 25384-2021 artfynd.xlsx
+++ b/artfynd/A 25384-2021 artfynd.xlsx
@@ -1815,7 +1815,7 @@
         <v>113679332</v>
       </c>
       <c r="B12" t="n">
-        <v>80462</v>
+        <v>80463</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>113679309</v>
       </c>
       <c r="B13" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>113679317</v>
       </c>
       <c r="B14" t="n">
-        <v>80433</v>
+        <v>80434</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>113679324</v>
       </c>
       <c r="B16" t="n">
-        <v>80393</v>
+        <v>80394</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>113679305</v>
       </c>
       <c r="B17" t="n">
-        <v>79360</v>
+        <v>79361</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>113679295</v>
       </c>
       <c r="B19" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>113680810</v>
       </c>
       <c r="B20" t="n">
-        <v>91875</v>
+        <v>91876</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>113680806</v>
       </c>
       <c r="B21" t="n">
-        <v>91912</v>
+        <v>91913</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>113679311</v>
       </c>
       <c r="B22" t="n">
-        <v>80433</v>
+        <v>80434</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>113680809</v>
       </c>
       <c r="B24" t="n">
-        <v>91875</v>
+        <v>91876</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>113680807</v>
       </c>
       <c r="B25" t="n">
-        <v>91926</v>
+        <v>91927</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>113680811</v>
       </c>
       <c r="B26" t="n">
-        <v>91912</v>
+        <v>91913</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>113679338</v>
       </c>
       <c r="B27" t="n">
-        <v>81313</v>
+        <v>81314</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>113679344</v>
       </c>
       <c r="B28" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>113679343</v>
       </c>
       <c r="B29" t="n">
-        <v>80393</v>
+        <v>80394</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>113679307</v>
       </c>
       <c r="B30" t="n">
-        <v>79360</v>
+        <v>79361</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>113679347</v>
       </c>
       <c r="B31" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>113680802</v>
       </c>
       <c r="B32" t="n">
-        <v>91875</v>
+        <v>91876</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>113679346</v>
       </c>
       <c r="B33" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
         <v>113679345</v>
       </c>
       <c r="B34" t="n">
-        <v>83310</v>
+        <v>83311</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>113679301</v>
       </c>
       <c r="B35" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>113679300</v>
       </c>
       <c r="B37" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>113679328</v>
       </c>
       <c r="B39" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>113679329</v>
       </c>
       <c r="B40" t="n">
-        <v>80393</v>
+        <v>80394</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>113679322</v>
       </c>
       <c r="B41" t="n">
-        <v>80393</v>
+        <v>80394</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         <v>113679308</v>
       </c>
       <c r="B42" t="n">
-        <v>79360</v>
+        <v>79361</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>113679314</v>
       </c>
       <c r="B43" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>113680812</v>
       </c>
       <c r="B44" t="n">
-        <v>91923</v>
+        <v>91924</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>113680808</v>
       </c>
       <c r="B45" t="n">
-        <v>91926</v>
+        <v>91927</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>113679341</v>
       </c>
       <c r="B47" t="n">
-        <v>80433</v>
+        <v>80434</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>113679340</v>
       </c>
       <c r="B48" t="n">
-        <v>80337</v>
+        <v>80338</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>113679323</v>
       </c>
       <c r="B51" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         <v>113680803</v>
       </c>
       <c r="B52" t="n">
-        <v>91875</v>
+        <v>91876</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>113679316</v>
       </c>
       <c r="B53" t="n">
-        <v>80393</v>
+        <v>80394</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
         <v>113679333</v>
       </c>
       <c r="B54" t="n">
-        <v>80393</v>
+        <v>80394</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>113679321</v>
       </c>
       <c r="B55" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         <v>113679303</v>
       </c>
       <c r="B56" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         <v>113679298</v>
       </c>
       <c r="B58" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>113680814</v>
       </c>
       <c r="B59" t="n">
-        <v>83176</v>
+        <v>83177</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>113682723</v>
       </c>
       <c r="B61" t="n">
-        <v>99143</v>
+        <v>99144</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>113679304</v>
       </c>
       <c r="B63" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>113680813</v>
       </c>
       <c r="B65" t="n">
-        <v>89295</v>
+        <v>89296</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>113680805</v>
       </c>
       <c r="B66" t="n">
-        <v>83176</v>
+        <v>83177</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         <v>113679320</v>
       </c>
       <c r="B67" t="n">
-        <v>79584</v>
+        <v>79585</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7751,7 +7751,7 @@
         <v>113679331</v>
       </c>
       <c r="B68" t="n">
-        <v>80462</v>
+        <v>80463</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>113679339</v>
       </c>
       <c r="B70" t="n">
-        <v>79360</v>
+        <v>79361</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>113680801</v>
       </c>
       <c r="B71" t="n">
-        <v>83176</v>
+        <v>83177</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>113679336</v>
       </c>
       <c r="B74" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>113680815</v>
       </c>
       <c r="B75" t="n">
-        <v>91875</v>
+        <v>91876</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         <v>113678090</v>
       </c>
       <c r="B76" t="n">
-        <v>96341</v>
+        <v>96342</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>113678091</v>
       </c>
       <c r="B77" t="n">
-        <v>95965</v>
+        <v>95966</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>113678088</v>
       </c>
       <c r="B78" t="n">
-        <v>96341</v>
+        <v>96342</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8917,7 +8917,7 @@
         <v>113678089</v>
       </c>
       <c r="B79" t="n">
-        <v>96341</v>
+        <v>96342</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>113678087</v>
       </c>
       <c r="B80" t="n">
-        <v>96341</v>
+        <v>96342</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>113682720</v>
       </c>
       <c r="B81" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9248,7 +9248,7 @@
         <v>113682717</v>
       </c>
       <c r="B82" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>113682729</v>
       </c>
       <c r="B83" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>113682725</v>
       </c>
       <c r="B84" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         <v>113682716</v>
       </c>
       <c r="B85" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9724,7 +9724,7 @@
         <v>113682728</v>
       </c>
       <c r="B86" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         <v>113682715</v>
       </c>
       <c r="B87" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9962,7 +9962,7 @@
         <v>113682722</v>
       </c>
       <c r="B88" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10081,7 +10081,7 @@
         <v>113682719</v>
       </c>
       <c r="B89" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10200,7 +10200,7 @@
         <v>113682721</v>
       </c>
       <c r="B90" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         <v>113682730</v>
       </c>
       <c r="B91" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>113682718</v>
       </c>
       <c r="B92" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>113682727</v>
       </c>
       <c r="B93" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         <v>113682726</v>
       </c>
       <c r="B94" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 25384-2021 artfynd.xlsx
+++ b/artfynd/A 25384-2021 artfynd.xlsx
@@ -1497,7 +1497,7 @@
         <v>113679334</v>
       </c>
       <c r="B9" t="n">
-        <v>75429</v>
+        <v>75432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>113679318</v>
       </c>
       <c r="B10" t="n">
-        <v>75429</v>
+        <v>75432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>113679313</v>
       </c>
       <c r="B11" t="n">
-        <v>75429</v>
+        <v>75432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>113679332</v>
       </c>
       <c r="B12" t="n">
-        <v>80463</v>
+        <v>80466</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>113679309</v>
       </c>
       <c r="B13" t="n">
-        <v>79329</v>
+        <v>79332</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>113679317</v>
       </c>
       <c r="B14" t="n">
-        <v>80434</v>
+        <v>80437</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>113679325</v>
       </c>
       <c r="B15" t="n">
-        <v>75429</v>
+        <v>75432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>113679324</v>
       </c>
       <c r="B16" t="n">
-        <v>80394</v>
+        <v>80397</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>113679305</v>
       </c>
       <c r="B17" t="n">
-        <v>79361</v>
+        <v>79364</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>113679337</v>
       </c>
       <c r="B18" t="n">
-        <v>75429</v>
+        <v>75432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>113679295</v>
       </c>
       <c r="B19" t="n">
-        <v>79329</v>
+        <v>79332</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>113680810</v>
       </c>
       <c r="B20" t="n">
-        <v>91876</v>
+        <v>91879</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>113680806</v>
       </c>
       <c r="B21" t="n">
-        <v>91913</v>
+        <v>91916</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>113679311</v>
       </c>
       <c r="B22" t="n">
-        <v>80434</v>
+        <v>80437</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>113679327</v>
       </c>
       <c r="B23" t="n">
-        <v>75429</v>
+        <v>75432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>113680809</v>
       </c>
       <c r="B24" t="n">
-        <v>91876</v>
+        <v>91879</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>113680807</v>
       </c>
       <c r="B25" t="n">
-        <v>91927</v>
+        <v>91930</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>113680811</v>
       </c>
       <c r="B26" t="n">
-        <v>91913</v>
+        <v>91916</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>113679338</v>
       </c>
       <c r="B27" t="n">
-        <v>81314</v>
+        <v>81317</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>113679344</v>
       </c>
       <c r="B28" t="n">
-        <v>79329</v>
+        <v>79332</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>113679343</v>
       </c>
       <c r="B29" t="n">
-        <v>80394</v>
+        <v>80397</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>113679307</v>
       </c>
       <c r="B30" t="n">
-        <v>79361</v>
+        <v>79364</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>113679347</v>
       </c>
       <c r="B31" t="n">
-        <v>79329</v>
+        <v>79332</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>113680802</v>
       </c>
       <c r="B32" t="n">
-        <v>91876</v>
+        <v>91879</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>113679346</v>
       </c>
       <c r="B33" t="n">
-        <v>79329</v>
+        <v>79332</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
         <v>113679345</v>
       </c>
       <c r="B34" t="n">
-        <v>83311</v>
+        <v>83314</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>113679301</v>
       </c>
       <c r="B35" t="n">
-        <v>79329</v>
+        <v>79332</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>113679335</v>
       </c>
       <c r="B36" t="n">
-        <v>75429</v>
+        <v>75432</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>113679300</v>
       </c>
       <c r="B37" t="n">
-        <v>79329</v>
+        <v>79332</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>113679297</v>
       </c>
       <c r="B38" t="n">
-        <v>75429</v>
+        <v>75432</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>113679328</v>
       </c>
       <c r="B39" t="n">
-        <v>79329</v>
+        <v>79332</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>113679329</v>
       </c>
       <c r="B40" t="n">
-        <v>80394</v>
+        <v>80397</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>113679322</v>
       </c>
       <c r="B41" t="n">
-        <v>80394</v>
+        <v>80397</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         <v>113679308</v>
       </c>
       <c r="B42" t="n">
-        <v>79361</v>
+        <v>79364</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>113679314</v>
       </c>
       <c r="B43" t="n">
-        <v>79329</v>
+        <v>79332</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>113680812</v>
       </c>
       <c r="B44" t="n">
-        <v>91924</v>
+        <v>91927</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>113680808</v>
       </c>
       <c r="B45" t="n">
-        <v>91927</v>
+        <v>91930</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         <v>113679312</v>
       </c>
       <c r="B46" t="n">
-        <v>75429</v>
+        <v>75432</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>113679341</v>
       </c>
       <c r="B47" t="n">
-        <v>80434</v>
+        <v>80437</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>113679340</v>
       </c>
       <c r="B48" t="n">
-        <v>80338</v>
+        <v>80341</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>113679323</v>
       </c>
       <c r="B51" t="n">
-        <v>79329</v>
+        <v>79332</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         <v>113680803</v>
       </c>
       <c r="B52" t="n">
-        <v>91876</v>
+        <v>91879</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>113679316</v>
       </c>
       <c r="B53" t="n">
-        <v>80394</v>
+        <v>80397</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
         <v>113679333</v>
       </c>
       <c r="B54" t="n">
-        <v>80394</v>
+        <v>80397</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>113679321</v>
       </c>
       <c r="B55" t="n">
-        <v>79329</v>
+        <v>79332</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         <v>113679303</v>
       </c>
       <c r="B56" t="n">
-        <v>79329</v>
+        <v>79332</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>113679302</v>
       </c>
       <c r="B57" t="n">
-        <v>75429</v>
+        <v>75432</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         <v>113679298</v>
       </c>
       <c r="B58" t="n">
-        <v>79329</v>
+        <v>79332</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>113680814</v>
       </c>
       <c r="B59" t="n">
-        <v>83177</v>
+        <v>83180</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>113679296</v>
       </c>
       <c r="B60" t="n">
-        <v>75429</v>
+        <v>75432</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>113682723</v>
       </c>
       <c r="B61" t="n">
-        <v>99144</v>
+        <v>99147</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>113679304</v>
       </c>
       <c r="B63" t="n">
-        <v>79329</v>
+        <v>79332</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7327,7 +7327,7 @@
         <v>113679310</v>
       </c>
       <c r="B64" t="n">
-        <v>75429</v>
+        <v>75432</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>113680813</v>
       </c>
       <c r="B65" t="n">
-        <v>89296</v>
+        <v>89299</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>113680805</v>
       </c>
       <c r="B66" t="n">
-        <v>83177</v>
+        <v>83180</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         <v>113679320</v>
       </c>
       <c r="B67" t="n">
-        <v>79585</v>
+        <v>79588</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7751,7 +7751,7 @@
         <v>113679331</v>
       </c>
       <c r="B68" t="n">
-        <v>80463</v>
+        <v>80466</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7857,7 +7857,7 @@
         <v>113679299</v>
       </c>
       <c r="B69" t="n">
-        <v>75429</v>
+        <v>75432</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>113679339</v>
       </c>
       <c r="B70" t="n">
-        <v>79361</v>
+        <v>79364</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>113680801</v>
       </c>
       <c r="B71" t="n">
-        <v>83177</v>
+        <v>83180</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8175,7 +8175,7 @@
         <v>113679326</v>
       </c>
       <c r="B72" t="n">
-        <v>75429</v>
+        <v>75432</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>113679342</v>
       </c>
       <c r="B73" t="n">
-        <v>75429</v>
+        <v>75432</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>113679336</v>
       </c>
       <c r="B74" t="n">
-        <v>79329</v>
+        <v>79332</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>113680815</v>
       </c>
       <c r="B75" t="n">
-        <v>91876</v>
+        <v>91879</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         <v>113678090</v>
       </c>
       <c r="B76" t="n">
-        <v>96342</v>
+        <v>96345</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>113678091</v>
       </c>
       <c r="B77" t="n">
-        <v>95966</v>
+        <v>95969</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>113678088</v>
       </c>
       <c r="B78" t="n">
-        <v>96342</v>
+        <v>96345</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8917,7 +8917,7 @@
         <v>113678089</v>
       </c>
       <c r="B79" t="n">
-        <v>96342</v>
+        <v>96345</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>113678087</v>
       </c>
       <c r="B80" t="n">
-        <v>96342</v>
+        <v>96345</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>113682720</v>
       </c>
       <c r="B81" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9248,7 +9248,7 @@
         <v>113682717</v>
       </c>
       <c r="B82" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>113682729</v>
       </c>
       <c r="B83" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>113682725</v>
       </c>
       <c r="B84" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         <v>113682716</v>
       </c>
       <c r="B85" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9724,7 +9724,7 @@
         <v>113682728</v>
       </c>
       <c r="B86" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         <v>113682715</v>
       </c>
       <c r="B87" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9962,7 +9962,7 @@
         <v>113682722</v>
       </c>
       <c r="B88" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10081,7 +10081,7 @@
         <v>113682719</v>
       </c>
       <c r="B89" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10200,7 +10200,7 @@
         <v>113682721</v>
       </c>
       <c r="B90" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         <v>113682730</v>
       </c>
       <c r="B91" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>113682718</v>
       </c>
       <c r="B92" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>113682727</v>
       </c>
       <c r="B93" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         <v>113682726</v>
       </c>
       <c r="B94" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
